--- a/Base/Backlog_38.xlsx
+++ b/Base/Backlog_38.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F83DF-1526-44AB-BF10-C1CE92D8FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DCE492-F3AA-46C4-9FEA-288C242A35CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="SPN" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -254,17 +254,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -286,7 +282,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -603,59 +622,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.5703125" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.5703125" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>11</v>
       </c>
@@ -665,22 +685,22 @@
       <c r="C2" s="13">
         <v>2025</v>
       </c>
-      <c r="D2" s="7">
-        <v>38</v>
-      </c>
-      <c r="E2" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="D2" s="14">
+        <v>38</v>
+      </c>
+      <c r="E2" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F2" s="16">
         <v>45926</v>
       </c>
       <c r="G2" s="13">
         <v>1261</v>
       </c>
-      <c r="H2" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I2" s="8">
+      <c r="H2" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I2" s="15">
         <v>45922</v>
       </c>
       <c r="J2" s="13" t="s">
@@ -690,7 +710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -700,22 +720,22 @@
       <c r="C3" s="13">
         <v>2025</v>
       </c>
-      <c r="D3" s="7">
-        <v>38</v>
-      </c>
-      <c r="E3" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F3" s="9">
+      <c r="D3" s="14">
+        <v>38</v>
+      </c>
+      <c r="E3" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F3" s="16">
         <v>45926</v>
       </c>
       <c r="G3" s="13">
         <v>1464</v>
       </c>
-      <c r="H3" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I3" s="8">
+      <c r="H3" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I3" s="15">
         <v>45922</v>
       </c>
       <c r="J3" s="13" t="s">
@@ -725,7 +745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>11</v>
       </c>
@@ -735,22 +755,22 @@
       <c r="C4" s="13">
         <v>2025</v>
       </c>
-      <c r="D4" s="7">
-        <v>38</v>
-      </c>
-      <c r="E4" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F4" s="9">
+      <c r="D4" s="14">
+        <v>38</v>
+      </c>
+      <c r="E4" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F4" s="16">
         <v>45926</v>
       </c>
       <c r="G4" s="13">
         <v>1558</v>
       </c>
-      <c r="H4" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I4" s="8">
+      <c r="H4" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I4" s="15">
         <v>45922</v>
       </c>
       <c r="J4" s="13" t="s">
@@ -760,7 +780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
@@ -770,22 +790,22 @@
       <c r="C5" s="13">
         <v>2025</v>
       </c>
-      <c r="D5" s="7">
-        <v>38</v>
-      </c>
-      <c r="E5" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="D5" s="14">
+        <v>38</v>
+      </c>
+      <c r="E5" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F5" s="16">
         <v>45926</v>
       </c>
       <c r="G5" s="13">
         <v>1748</v>
       </c>
-      <c r="H5" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I5" s="8">
+      <c r="H5" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I5" s="15">
         <v>45922</v>
       </c>
       <c r="J5" s="13" t="s">
@@ -795,7 +815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
@@ -805,22 +825,22 @@
       <c r="C6" s="13">
         <v>2025</v>
       </c>
-      <c r="D6" s="7">
-        <v>38</v>
-      </c>
-      <c r="E6" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="D6" s="14">
+        <v>38</v>
+      </c>
+      <c r="E6" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F6" s="16">
         <v>45926</v>
       </c>
       <c r="G6" s="13">
         <v>1835</v>
       </c>
-      <c r="H6" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="H6" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I6" s="15">
         <v>45922</v>
       </c>
       <c r="J6" s="13" t="s">
@@ -830,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
@@ -840,22 +860,22 @@
       <c r="C7" s="13">
         <v>2025</v>
       </c>
-      <c r="D7" s="7">
-        <v>38</v>
-      </c>
-      <c r="E7" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="D7" s="14">
+        <v>38</v>
+      </c>
+      <c r="E7" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F7" s="16">
         <v>45926</v>
       </c>
       <c r="G7" s="13">
         <v>2006</v>
       </c>
-      <c r="H7" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="H7" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I7" s="15">
         <v>45922</v>
       </c>
       <c r="J7" s="13" t="s">
@@ -865,7 +885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
@@ -875,22 +895,22 @@
       <c r="C8" s="13">
         <v>2025</v>
       </c>
-      <c r="D8" s="7">
-        <v>38</v>
-      </c>
-      <c r="E8" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="D8" s="14">
+        <v>38</v>
+      </c>
+      <c r="E8" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F8" s="16">
         <v>45926</v>
       </c>
       <c r="G8" s="13">
         <v>2174</v>
       </c>
-      <c r="H8" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I8" s="8">
+      <c r="H8" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I8" s="15">
         <v>45922</v>
       </c>
       <c r="J8" s="13" t="s">
@@ -900,7 +920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
@@ -910,22 +930,22 @@
       <c r="C9" s="13">
         <v>2025</v>
       </c>
-      <c r="D9" s="7">
-        <v>38</v>
-      </c>
-      <c r="E9" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="D9" s="14">
+        <v>38</v>
+      </c>
+      <c r="E9" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F9" s="16">
         <v>45926</v>
       </c>
       <c r="G9" s="13">
         <v>2179</v>
       </c>
-      <c r="H9" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="H9" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I9" s="15">
         <v>45922</v>
       </c>
       <c r="J9" s="13" t="s">
@@ -935,7 +955,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>11</v>
       </c>
@@ -945,22 +965,22 @@
       <c r="C10" s="13">
         <v>2025</v>
       </c>
-      <c r="D10" s="7">
-        <v>38</v>
-      </c>
-      <c r="E10" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="D10" s="14">
+        <v>38</v>
+      </c>
+      <c r="E10" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F10" s="16">
         <v>45926</v>
       </c>
       <c r="G10" s="13">
         <v>2237</v>
       </c>
-      <c r="H10" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I10" s="8">
+      <c r="H10" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I10" s="15">
         <v>45922</v>
       </c>
       <c r="J10" s="13" t="s">
@@ -970,7 +990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>11</v>
       </c>
@@ -980,22 +1000,22 @@
       <c r="C11" s="13">
         <v>2025</v>
       </c>
-      <c r="D11" s="7">
-        <v>38</v>
-      </c>
-      <c r="E11" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="D11" s="14">
+        <v>38</v>
+      </c>
+      <c r="E11" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F11" s="16">
         <v>45926</v>
       </c>
       <c r="G11" s="13">
         <v>2366</v>
       </c>
-      <c r="H11" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="H11" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I11" s="15">
         <v>45922</v>
       </c>
       <c r="J11" s="13" t="s">
@@ -1005,7 +1025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>11</v>
       </c>
@@ -1015,22 +1035,22 @@
       <c r="C12" s="13">
         <v>2025</v>
       </c>
-      <c r="D12" s="7">
-        <v>38</v>
-      </c>
-      <c r="E12" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="D12" s="14">
+        <v>38</v>
+      </c>
+      <c r="E12" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F12" s="16">
         <v>45926</v>
       </c>
       <c r="G12" s="13">
         <v>1102</v>
       </c>
-      <c r="H12" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I12" s="8">
+      <c r="H12" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I12" s="15">
         <v>45922</v>
       </c>
       <c r="J12" s="13" t="s">
@@ -1040,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1050,22 +1070,22 @@
       <c r="C13" s="13">
         <v>2025</v>
       </c>
-      <c r="D13" s="7">
-        <v>38</v>
-      </c>
-      <c r="E13" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="D13" s="14">
+        <v>38</v>
+      </c>
+      <c r="E13" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F13" s="16">
         <v>45926</v>
       </c>
       <c r="G13" s="13">
         <v>1734</v>
       </c>
-      <c r="H13" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="H13" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I13" s="15">
         <v>45922</v>
       </c>
       <c r="J13" s="13" t="s">
@@ -1075,7 +1095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
@@ -1085,22 +1105,22 @@
       <c r="C14" s="13">
         <v>2025</v>
       </c>
-      <c r="D14" s="7">
-        <v>38</v>
-      </c>
-      <c r="E14" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F14" s="9">
+      <c r="D14" s="14">
+        <v>38</v>
+      </c>
+      <c r="E14" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F14" s="16">
         <v>45926</v>
       </c>
       <c r="G14" s="13">
         <v>1743</v>
       </c>
-      <c r="H14" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I14" s="8">
+      <c r="H14" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I14" s="15">
         <v>45922</v>
       </c>
       <c r="J14" s="13" t="s">
@@ -1110,7 +1130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
@@ -1120,22 +1140,22 @@
       <c r="C15" s="13">
         <v>2025</v>
       </c>
-      <c r="D15" s="7">
-        <v>38</v>
-      </c>
-      <c r="E15" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F15" s="9">
+      <c r="D15" s="14">
+        <v>38</v>
+      </c>
+      <c r="E15" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F15" s="16">
         <v>45926</v>
       </c>
       <c r="G15" s="13">
         <v>2248</v>
       </c>
-      <c r="H15" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="H15" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I15" s="15">
         <v>45922</v>
       </c>
       <c r="J15" s="13" t="s">
@@ -1145,7 +1165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
@@ -1155,22 +1175,22 @@
       <c r="C16" s="13">
         <v>2025</v>
       </c>
-      <c r="D16" s="7">
-        <v>38</v>
-      </c>
-      <c r="E16" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="D16" s="14">
+        <v>38</v>
+      </c>
+      <c r="E16" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F16" s="16">
         <v>45926</v>
       </c>
       <c r="G16" s="13">
         <v>2279</v>
       </c>
-      <c r="H16" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="H16" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I16" s="15">
         <v>45922</v>
       </c>
       <c r="J16" s="13" t="s">
@@ -1180,7 +1200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -1190,22 +1210,22 @@
       <c r="C17" s="13">
         <v>2025</v>
       </c>
-      <c r="D17" s="7">
-        <v>38</v>
-      </c>
-      <c r="E17" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F17" s="9">
+      <c r="D17" s="14">
+        <v>38</v>
+      </c>
+      <c r="E17" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F17" s="16">
         <v>45926</v>
       </c>
       <c r="G17" s="13">
         <v>2490</v>
       </c>
-      <c r="H17" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I17" s="8">
+      <c r="H17" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I17" s="15">
         <v>45922</v>
       </c>
       <c r="J17" s="13" t="s">
@@ -1215,7 +1235,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
@@ -1225,22 +1245,22 @@
       <c r="C18" s="13">
         <v>2025</v>
       </c>
-      <c r="D18" s="7">
-        <v>38</v>
-      </c>
-      <c r="E18" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F18" s="9">
+      <c r="D18" s="14">
+        <v>38</v>
+      </c>
+      <c r="E18" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F18" s="16">
         <v>45926</v>
       </c>
       <c r="G18" s="13">
         <v>2529</v>
       </c>
-      <c r="H18" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I18" s="8">
+      <c r="H18" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I18" s="15">
         <v>45922</v>
       </c>
       <c r="J18" s="13" t="s">
@@ -1250,7 +1270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
@@ -1260,22 +1280,22 @@
       <c r="C19" s="13">
         <v>2025</v>
       </c>
-      <c r="D19" s="7">
-        <v>38</v>
-      </c>
-      <c r="E19" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F19" s="9">
+      <c r="D19" s="14">
+        <v>38</v>
+      </c>
+      <c r="E19" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F19" s="16">
         <v>45926</v>
       </c>
       <c r="G19" s="13">
         <v>2581</v>
       </c>
-      <c r="H19" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I19" s="8">
+      <c r="H19" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I19" s="15">
         <v>45922</v>
       </c>
       <c r="J19" s="13" t="s">
@@ -1285,7 +1305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
@@ -1295,22 +1315,22 @@
       <c r="C20" s="13">
         <v>2025</v>
       </c>
-      <c r="D20" s="7">
-        <v>38</v>
-      </c>
-      <c r="E20" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="D20" s="14">
+        <v>38</v>
+      </c>
+      <c r="E20" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F20" s="16">
         <v>45926</v>
       </c>
       <c r="G20" s="13">
         <v>1159</v>
       </c>
-      <c r="H20" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I20" s="8">
+      <c r="H20" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I20" s="15">
         <v>45922</v>
       </c>
       <c r="J20" s="13" t="s">
@@ -1320,7 +1340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>11</v>
       </c>
@@ -1330,22 +1350,22 @@
       <c r="C21" s="13">
         <v>2025</v>
       </c>
-      <c r="D21" s="7">
-        <v>38</v>
-      </c>
-      <c r="E21" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F21" s="9">
+      <c r="D21" s="14">
+        <v>38</v>
+      </c>
+      <c r="E21" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F21" s="16">
         <v>45926</v>
       </c>
       <c r="G21" s="13">
         <v>2051</v>
       </c>
-      <c r="H21" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I21" s="8">
+      <c r="H21" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I21" s="15">
         <v>45922</v>
       </c>
       <c r="J21" s="13" t="s">
@@ -1355,7 +1375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>11</v>
       </c>
@@ -1365,22 +1385,22 @@
       <c r="C22" s="13">
         <v>2025</v>
       </c>
-      <c r="D22" s="7">
-        <v>38</v>
-      </c>
-      <c r="E22" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F22" s="9">
+      <c r="D22" s="14">
+        <v>38</v>
+      </c>
+      <c r="E22" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F22" s="16">
         <v>45926</v>
       </c>
       <c r="G22" s="13">
         <v>2095</v>
       </c>
-      <c r="H22" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I22" s="8">
+      <c r="H22" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I22" s="15">
         <v>45922</v>
       </c>
       <c r="J22" s="13" t="s">
@@ -1390,7 +1410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>11</v>
       </c>
@@ -1400,22 +1420,22 @@
       <c r="C23" s="13">
         <v>2025</v>
       </c>
-      <c r="D23" s="7">
-        <v>38</v>
-      </c>
-      <c r="E23" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F23" s="9">
+      <c r="D23" s="14">
+        <v>38</v>
+      </c>
+      <c r="E23" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F23" s="16">
         <v>45926</v>
       </c>
       <c r="G23" s="13">
         <v>2270</v>
       </c>
-      <c r="H23" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="H23" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I23" s="15">
         <v>45922</v>
       </c>
       <c r="J23" s="13" t="s">
@@ -1425,7 +1445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>11</v>
       </c>
@@ -1435,22 +1455,22 @@
       <c r="C24" s="13">
         <v>2025</v>
       </c>
-      <c r="D24" s="7">
-        <v>38</v>
-      </c>
-      <c r="E24" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F24" s="9">
+      <c r="D24" s="14">
+        <v>38</v>
+      </c>
+      <c r="E24" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F24" s="16">
         <v>45926</v>
       </c>
       <c r="G24" s="13">
         <v>2231</v>
       </c>
-      <c r="H24" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I24" s="8">
+      <c r="H24" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I24" s="15">
         <v>45922</v>
       </c>
       <c r="J24" s="13" t="s">
@@ -1460,7 +1480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>11</v>
       </c>
@@ -1470,22 +1490,22 @@
       <c r="C25" s="13">
         <v>2025</v>
       </c>
-      <c r="D25" s="7">
-        <v>38</v>
-      </c>
-      <c r="E25" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="D25" s="14">
+        <v>38</v>
+      </c>
+      <c r="E25" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F25" s="16">
         <v>45926</v>
       </c>
       <c r="G25" s="13">
         <v>2458</v>
       </c>
-      <c r="H25" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I25" s="8">
+      <c r="H25" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I25" s="15">
         <v>45922</v>
       </c>
       <c r="J25" s="13" t="s">
@@ -1495,7 +1515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>11</v>
       </c>
@@ -1505,22 +1525,22 @@
       <c r="C26" s="13">
         <v>2025</v>
       </c>
-      <c r="D26" s="7">
-        <v>38</v>
-      </c>
-      <c r="E26" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F26" s="9">
+      <c r="D26" s="14">
+        <v>38</v>
+      </c>
+      <c r="E26" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F26" s="16">
         <v>45926</v>
       </c>
       <c r="G26" s="13">
         <v>1010</v>
       </c>
-      <c r="H26" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I26" s="8">
+      <c r="H26" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I26" s="15">
         <v>45922</v>
       </c>
       <c r="J26" s="13" t="s">
@@ -1530,7 +1550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>11</v>
       </c>
@@ -1540,22 +1560,22 @@
       <c r="C27" s="13">
         <v>2025</v>
       </c>
-      <c r="D27" s="7">
-        <v>38</v>
-      </c>
-      <c r="E27" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F27" s="9">
+      <c r="D27" s="14">
+        <v>38</v>
+      </c>
+      <c r="E27" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F27" s="16">
         <v>45926</v>
       </c>
       <c r="G27" s="13">
         <v>1535</v>
       </c>
-      <c r="H27" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I27" s="8">
+      <c r="H27" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I27" s="15">
         <v>45922</v>
       </c>
       <c r="J27" s="13" t="s">
@@ -1565,7 +1585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>11</v>
       </c>
@@ -1575,22 +1595,22 @@
       <c r="C28" s="13">
         <v>2025</v>
       </c>
-      <c r="D28" s="7">
-        <v>38</v>
-      </c>
-      <c r="E28" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="D28" s="14">
+        <v>38</v>
+      </c>
+      <c r="E28" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F28" s="16">
         <v>45926</v>
       </c>
       <c r="G28" s="13">
         <v>1802</v>
       </c>
-      <c r="H28" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I28" s="8">
+      <c r="H28" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I28" s="15">
         <v>45922</v>
       </c>
       <c r="J28" s="13" t="s">
@@ -1600,7 +1620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>11</v>
       </c>
@@ -1610,22 +1630,22 @@
       <c r="C29" s="13">
         <v>2025</v>
       </c>
-      <c r="D29" s="7">
-        <v>38</v>
-      </c>
-      <c r="E29" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F29" s="9">
+      <c r="D29" s="14">
+        <v>38</v>
+      </c>
+      <c r="E29" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F29" s="16">
         <v>45926</v>
       </c>
       <c r="G29" s="13">
         <v>2010</v>
       </c>
-      <c r="H29" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="H29" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I29" s="15">
         <v>45922</v>
       </c>
       <c r="J29" s="13" t="s">
@@ -1635,7 +1655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>11</v>
       </c>
@@ -1645,22 +1665,22 @@
       <c r="C30" s="13">
         <v>2025</v>
       </c>
-      <c r="D30" s="7">
-        <v>38</v>
-      </c>
-      <c r="E30" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F30" s="9">
+      <c r="D30" s="14">
+        <v>38</v>
+      </c>
+      <c r="E30" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F30" s="16">
         <v>45926</v>
       </c>
       <c r="G30" s="13">
         <v>344208</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="17">
         <v>45870</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="15">
         <v>45922</v>
       </c>
       <c r="J30" s="13" t="s">
@@ -1670,7 +1690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>11</v>
       </c>
@@ -1680,22 +1700,22 @@
       <c r="C31" s="13">
         <v>2025</v>
       </c>
-      <c r="D31" s="7">
-        <v>38</v>
-      </c>
-      <c r="E31" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F31" s="9">
+      <c r="D31" s="14">
+        <v>38</v>
+      </c>
+      <c r="E31" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F31" s="16">
         <v>45926</v>
       </c>
       <c r="G31" s="13">
         <v>2468</v>
       </c>
-      <c r="H31" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I31" s="8">
+      <c r="H31" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I31" s="15">
         <v>45922</v>
       </c>
       <c r="J31" s="13" t="s">
@@ -1705,7 +1725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>11</v>
       </c>
@@ -1715,22 +1735,22 @@
       <c r="C32" s="13">
         <v>2025</v>
       </c>
-      <c r="D32" s="7">
-        <v>38</v>
-      </c>
-      <c r="E32" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F32" s="9">
+      <c r="D32" s="14">
+        <v>38</v>
+      </c>
+      <c r="E32" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F32" s="16">
         <v>45926</v>
       </c>
       <c r="G32" s="13">
         <v>2518</v>
       </c>
-      <c r="H32" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I32" s="8">
+      <c r="H32" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I32" s="15">
         <v>45922</v>
       </c>
       <c r="J32" s="13" t="s">
@@ -1740,7 +1760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>11</v>
       </c>
@@ -1753,19 +1773,19 @@
       <c r="D33" s="13">
         <v>38</v>
       </c>
-      <c r="E33" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F33" s="9">
+      <c r="E33" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F33" s="16">
         <v>45926</v>
       </c>
       <c r="G33" s="13">
         <v>1045</v>
       </c>
-      <c r="H33" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I33" s="8">
+      <c r="H33" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I33" s="15">
         <v>45922</v>
       </c>
       <c r="J33" s="13" t="s">
@@ -1775,7 +1795,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>11</v>
       </c>
@@ -1788,19 +1808,19 @@
       <c r="D34" s="13">
         <v>38</v>
       </c>
-      <c r="E34" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F34" s="9">
+      <c r="E34" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F34" s="16">
         <v>45926</v>
       </c>
       <c r="G34" s="13">
         <v>344387</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="17">
         <v>45870</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="15">
         <v>45922</v>
       </c>
       <c r="J34" s="13" t="s">
@@ -1810,7 +1830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>11</v>
       </c>
@@ -1823,19 +1843,19 @@
       <c r="D35" s="13">
         <v>38</v>
       </c>
-      <c r="E35" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F35" s="9">
+      <c r="E35" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F35" s="16">
         <v>45926</v>
       </c>
       <c r="G35" s="13">
         <v>1720</v>
       </c>
-      <c r="H35" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I35" s="8">
+      <c r="H35" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I35" s="15">
         <v>45922</v>
       </c>
       <c r="J35" s="13" t="s">
@@ -1845,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>11</v>
       </c>
@@ -1858,19 +1878,19 @@
       <c r="D36" s="13">
         <v>38</v>
       </c>
-      <c r="E36" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F36" s="9">
+      <c r="E36" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F36" s="16">
         <v>45926</v>
       </c>
       <c r="G36" s="13">
         <v>2005</v>
       </c>
-      <c r="H36" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I36" s="8">
+      <c r="H36" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I36" s="15">
         <v>45922</v>
       </c>
       <c r="J36" s="13" t="s">
@@ -1880,7 +1900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>11</v>
       </c>
@@ -1893,19 +1913,19 @@
       <c r="D37" s="13">
         <v>38</v>
       </c>
-      <c r="E37" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F37" s="9">
+      <c r="E37" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F37" s="16">
         <v>45926</v>
       </c>
       <c r="G37" s="13">
         <v>2009</v>
       </c>
-      <c r="H37" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I37" s="8">
+      <c r="H37" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I37" s="15">
         <v>45922</v>
       </c>
       <c r="J37" s="13" t="s">
@@ -1915,7 +1935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>11</v>
       </c>
@@ -1928,19 +1948,19 @@
       <c r="D38" s="13">
         <v>38</v>
       </c>
-      <c r="E38" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F38" s="9">
+      <c r="E38" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F38" s="16">
         <v>45926</v>
       </c>
       <c r="G38" s="13">
         <v>2048</v>
       </c>
-      <c r="H38" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I38" s="8">
+      <c r="H38" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I38" s="15">
         <v>45922</v>
       </c>
       <c r="J38" s="13" t="s">
@@ -1950,7 +1970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>11</v>
       </c>
@@ -1963,19 +1983,19 @@
       <c r="D39" s="13">
         <v>38</v>
       </c>
-      <c r="E39" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F39" s="9">
+      <c r="E39" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F39" s="16">
         <v>45926</v>
       </c>
       <c r="G39" s="13">
         <v>2054</v>
       </c>
-      <c r="H39" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I39" s="8">
+      <c r="H39" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I39" s="15">
         <v>45922</v>
       </c>
       <c r="J39" s="13" t="s">
@@ -1985,7 +2005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>11</v>
       </c>
@@ -1998,19 +2018,19 @@
       <c r="D40" s="13">
         <v>38</v>
       </c>
-      <c r="E40" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F40" s="9">
+      <c r="E40" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F40" s="16">
         <v>45926</v>
       </c>
       <c r="G40" s="13">
         <v>2059</v>
       </c>
-      <c r="H40" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I40" s="8">
+      <c r="H40" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I40" s="15">
         <v>45922</v>
       </c>
       <c r="J40" s="13" t="s">
@@ -2020,7 +2040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>11</v>
       </c>
@@ -2033,19 +2053,19 @@
       <c r="D41" s="13">
         <v>38</v>
       </c>
-      <c r="E41" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F41" s="9">
+      <c r="E41" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F41" s="16">
         <v>45926</v>
       </c>
       <c r="G41" s="13">
         <v>2099</v>
       </c>
-      <c r="H41" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I41" s="8">
+      <c r="H41" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I41" s="15">
         <v>45922</v>
       </c>
       <c r="J41" s="13" t="s">
@@ -2055,7 +2075,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>11</v>
       </c>
@@ -2068,19 +2088,19 @@
       <c r="D42" s="13">
         <v>38</v>
       </c>
-      <c r="E42" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F42" s="9">
+      <c r="E42" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F42" s="16">
         <v>45926</v>
       </c>
       <c r="G42" s="13">
         <v>2100</v>
       </c>
-      <c r="H42" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I42" s="8">
+      <c r="H42" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I42" s="15">
         <v>45922</v>
       </c>
       <c r="J42" s="13" t="s">
@@ -2090,7 +2110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>11</v>
       </c>
@@ -2103,19 +2123,19 @@
       <c r="D43" s="13">
         <v>38</v>
       </c>
-      <c r="E43" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F43" s="9">
+      <c r="E43" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F43" s="16">
         <v>45926</v>
       </c>
       <c r="G43" s="13">
         <v>2134</v>
       </c>
-      <c r="H43" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I43" s="8">
+      <c r="H43" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I43" s="15">
         <v>45922</v>
       </c>
       <c r="J43" s="13" t="s">
@@ -2125,7 +2145,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>11</v>
       </c>
@@ -2138,19 +2158,19 @@
       <c r="D44" s="13">
         <v>38</v>
       </c>
-      <c r="E44" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F44" s="9">
+      <c r="E44" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F44" s="16">
         <v>45926</v>
       </c>
       <c r="G44" s="13">
         <v>2156</v>
       </c>
-      <c r="H44" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I44" s="8">
+      <c r="H44" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I44" s="15">
         <v>45922</v>
       </c>
       <c r="J44" s="13" t="s">
@@ -2160,7 +2180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>11</v>
       </c>
@@ -2173,19 +2193,19 @@
       <c r="D45" s="13">
         <v>38</v>
       </c>
-      <c r="E45" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F45" s="9">
+      <c r="E45" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F45" s="16">
         <v>45926</v>
       </c>
       <c r="G45" s="13">
         <v>2256</v>
       </c>
-      <c r="H45" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I45" s="8">
+      <c r="H45" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I45" s="15">
         <v>45922</v>
       </c>
       <c r="J45" s="13" t="s">
@@ -2195,7 +2215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>11</v>
       </c>
@@ -2208,19 +2228,19 @@
       <c r="D46" s="13">
         <v>38</v>
       </c>
-      <c r="E46" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F46" s="9">
+      <c r="E46" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F46" s="16">
         <v>45926</v>
       </c>
       <c r="G46" s="13">
         <v>2266</v>
       </c>
-      <c r="H46" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I46" s="8">
+      <c r="H46" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I46" s="15">
         <v>45922</v>
       </c>
       <c r="J46" s="13" t="s">
@@ -2230,7 +2250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>11</v>
       </c>
@@ -2243,19 +2263,19 @@
       <c r="D47" s="13">
         <v>38</v>
       </c>
-      <c r="E47" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F47" s="9">
+      <c r="E47" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F47" s="16">
         <v>45926</v>
       </c>
       <c r="G47" s="13">
         <v>2326</v>
       </c>
-      <c r="H47" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I47" s="8">
+      <c r="H47" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I47" s="15">
         <v>45922</v>
       </c>
       <c r="J47" s="13" t="s">
@@ -2265,7 +2285,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>11</v>
       </c>
@@ -2278,19 +2298,19 @@
       <c r="D48" s="13">
         <v>38</v>
       </c>
-      <c r="E48" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F48" s="9">
+      <c r="E48" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F48" s="16">
         <v>45926</v>
       </c>
       <c r="G48" s="13">
         <v>2411</v>
       </c>
-      <c r="H48" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I48" s="8">
+      <c r="H48" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I48" s="15">
         <v>45922</v>
       </c>
       <c r="J48" s="13" t="s">
@@ -2300,7 +2320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>11</v>
       </c>
@@ -2313,19 +2333,19 @@
       <c r="D49" s="13">
         <v>38</v>
       </c>
-      <c r="E49" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F49" s="9">
+      <c r="E49" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F49" s="16">
         <v>45926</v>
       </c>
       <c r="G49" s="13">
         <v>2591</v>
       </c>
-      <c r="H49" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I49" s="8">
+      <c r="H49" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I49" s="15">
         <v>45922</v>
       </c>
       <c r="J49" s="13" t="s">
@@ -2335,7 +2355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>11</v>
       </c>
@@ -2348,19 +2368,19 @@
       <c r="D50" s="13">
         <v>38</v>
       </c>
-      <c r="E50" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F50" s="9">
+      <c r="E50" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F50" s="16">
         <v>45926</v>
       </c>
       <c r="G50" s="13">
         <v>2440</v>
       </c>
-      <c r="H50" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I50" s="8">
+      <c r="H50" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I50" s="15">
         <v>45922</v>
       </c>
       <c r="J50" s="13" t="s">
@@ -2370,7 +2390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>11</v>
       </c>
@@ -2383,19 +2403,19 @@
       <c r="D51" s="13">
         <v>38</v>
       </c>
-      <c r="E51" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F51" s="9">
+      <c r="E51" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F51" s="16">
         <v>45926</v>
       </c>
       <c r="G51" s="13">
         <v>1838</v>
       </c>
-      <c r="H51" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I51" s="8">
+      <c r="H51" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I51" s="15">
         <v>45922</v>
       </c>
       <c r="J51" s="13" t="s">
@@ -2405,7 +2425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>11</v>
       </c>
@@ -2418,19 +2438,19 @@
       <c r="D52" s="13">
         <v>38</v>
       </c>
-      <c r="E52" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F52" s="9">
+      <c r="E52" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F52" s="16">
         <v>45926</v>
       </c>
       <c r="G52" s="13">
         <v>344437</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="17">
         <v>45870</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="15">
         <v>45922</v>
       </c>
       <c r="J52" s="13" t="s">
@@ -2440,7 +2460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>11</v>
       </c>
@@ -2453,19 +2473,19 @@
       <c r="D53" s="13">
         <v>38</v>
       </c>
-      <c r="E53" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F53" s="9">
+      <c r="E53" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F53" s="16">
         <v>45926</v>
       </c>
       <c r="G53" s="13">
         <v>344693</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="17">
         <v>45870</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="15">
         <v>45922</v>
       </c>
       <c r="J53" s="13" t="s">
@@ -2475,7 +2495,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>11</v>
       </c>
@@ -2488,19 +2508,19 @@
       <c r="D54" s="13">
         <v>38</v>
       </c>
-      <c r="E54" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F54" s="9">
+      <c r="E54" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F54" s="16">
         <v>45926</v>
       </c>
       <c r="G54" s="13">
         <v>1564</v>
       </c>
-      <c r="H54" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I54" s="8">
+      <c r="H54" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I54" s="15">
         <v>45922</v>
       </c>
       <c r="J54" s="13" t="s">
@@ -2510,7 +2530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>11</v>
       </c>
@@ -2523,19 +2543,19 @@
       <c r="D55" s="13">
         <v>38</v>
       </c>
-      <c r="E55" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F55" s="9">
+      <c r="E55" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F55" s="16">
         <v>45926</v>
       </c>
       <c r="G55" s="13">
         <v>1176</v>
       </c>
-      <c r="H55" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I55" s="8">
+      <c r="H55" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I55" s="15">
         <v>45922</v>
       </c>
       <c r="J55" s="13" t="s">
@@ -2545,7 +2565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>11</v>
       </c>
@@ -2558,19 +2578,19 @@
       <c r="D56" s="13">
         <v>38</v>
       </c>
-      <c r="E56" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F56" s="9">
+      <c r="E56" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F56" s="16">
         <v>45926</v>
       </c>
       <c r="G56" s="13">
         <v>1541</v>
       </c>
-      <c r="H56" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I56" s="8">
+      <c r="H56" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I56" s="15">
         <v>45922</v>
       </c>
       <c r="J56" s="13" t="s">
@@ -2580,7 +2600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>11</v>
       </c>
@@ -2593,19 +2613,19 @@
       <c r="D57" s="13">
         <v>38</v>
       </c>
-      <c r="E57" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F57" s="9">
+      <c r="E57" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F57" s="16">
         <v>45926</v>
       </c>
       <c r="G57" s="13">
         <v>2015</v>
       </c>
-      <c r="H57" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I57" s="8">
+      <c r="H57" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I57" s="15">
         <v>45922</v>
       </c>
       <c r="J57" s="13" t="s">
@@ -2615,7 +2635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>11</v>
       </c>
@@ -2628,19 +2648,19 @@
       <c r="D58" s="13">
         <v>38</v>
       </c>
-      <c r="E58" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F58" s="9">
+      <c r="E58" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F58" s="16">
         <v>45926</v>
       </c>
       <c r="G58" s="13">
         <v>2128</v>
       </c>
-      <c r="H58" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I58" s="8">
+      <c r="H58" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I58" s="15">
         <v>45922</v>
       </c>
       <c r="J58" s="13" t="s">
@@ -2650,7 +2670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>11</v>
       </c>
@@ -2663,19 +2683,19 @@
       <c r="D59" s="13">
         <v>38</v>
       </c>
-      <c r="E59" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F59" s="9">
+      <c r="E59" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F59" s="16">
         <v>45926</v>
       </c>
       <c r="G59" s="13">
         <v>2522</v>
       </c>
-      <c r="H59" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="H59" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I59" s="15">
         <v>45922</v>
       </c>
       <c r="J59" s="13" t="s">
@@ -2685,7 +2705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>11</v>
       </c>
@@ -2698,19 +2718,19 @@
       <c r="D60" s="13">
         <v>38</v>
       </c>
-      <c r="E60" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F60" s="9">
+      <c r="E60" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F60" s="16">
         <v>45926</v>
       </c>
       <c r="G60" s="13">
         <v>907</v>
       </c>
-      <c r="H60" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I60" s="8">
+      <c r="H60" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I60" s="15">
         <v>45922</v>
       </c>
       <c r="J60" s="13" t="s">
@@ -2720,7 +2740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>11</v>
       </c>
@@ -2733,19 +2753,19 @@
       <c r="D61" s="13">
         <v>38</v>
       </c>
-      <c r="E61" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F61" s="9">
+      <c r="E61" s="15">
+        <v>45922</v>
+      </c>
+      <c r="F61" s="16">
         <v>45926</v>
       </c>
       <c r="G61" s="13">
         <v>339211</v>
       </c>
-      <c r="H61" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I61" s="8">
+      <c r="H61" s="17">
+        <v>45901</v>
+      </c>
+      <c r="I61" s="15">
         <v>45922</v>
       </c>
       <c r="J61" s="13" t="s">
@@ -2756,47 +2776,53 @@
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="F62" s="20"/>
+      <c r="I62" s="20"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="F63" s="20"/>
+      <c r="I63" s="20"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="F64" s="20"/>
+      <c r="I64" s="20"/>
     </row>
     <row r="65" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="F65" s="20"/>
+      <c r="I65" s="20"/>
     </row>
     <row r="66" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="F66" s="20"/>
+      <c r="I66" s="20"/>
     </row>
     <row r="67" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="F67" s="20"/>
+      <c r="I67" s="20"/>
     </row>
     <row r="68" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="F68" s="20"/>
+      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="F69" s="20"/>
+      <c r="I69" s="20"/>
     </row>
     <row r="70" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="F70" s="20"/>
+      <c r="I70" s="20"/>
     </row>
     <row r="71" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="F71" s="20"/>
+      <c r="I71" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
+  <autoFilter ref="A1:K61" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <filterColumn colId="7">
+      <filters>
+        <dateGroupItem year="2025" month="8" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2822,492 +2848,492 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D2" s="7">
-        <v>38</v>
-      </c>
-      <c r="E2" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F2" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="C2" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="5">
+        <v>38</v>
+      </c>
+      <c r="E2" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F2" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G2" s="5">
         <v>2294</v>
       </c>
-      <c r="H2" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I2" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="H2" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I2" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="7">
-        <v>38</v>
-      </c>
-      <c r="E3" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F3" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="C3" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="5">
+        <v>38</v>
+      </c>
+      <c r="E3" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F3" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G3" s="5">
         <v>2513</v>
       </c>
-      <c r="H3" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I3" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="H3" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I3" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D4" s="7">
-        <v>38</v>
-      </c>
-      <c r="E4" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F4" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="C4" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="5">
+        <v>38</v>
+      </c>
+      <c r="E4" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G4" s="5">
         <v>2339</v>
       </c>
-      <c r="H4" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I4" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="H4" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I4" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D5" s="7">
-        <v>38</v>
-      </c>
-      <c r="E5" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F5" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="C5" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="5">
+        <v>38</v>
+      </c>
+      <c r="E5" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F5" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G5" s="5">
         <v>2273</v>
       </c>
-      <c r="H5" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I5" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="H5" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D6" s="7">
-        <v>38</v>
-      </c>
-      <c r="E6" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F6" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="C6" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D6" s="5">
+        <v>38</v>
+      </c>
+      <c r="E6" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F6" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G6" s="5">
         <v>2280</v>
       </c>
-      <c r="H6" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I6" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="H6" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D7" s="7">
-        <v>38</v>
-      </c>
-      <c r="E7" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F7" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="C7" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="5">
+        <v>38</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F7" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G7" s="5">
         <v>2364</v>
       </c>
-      <c r="H7" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I7" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="H7" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I7" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D8" s="7">
-        <v>38</v>
-      </c>
-      <c r="E8" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F8" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="C8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D8" s="5">
+        <v>38</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F8" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G8" s="5">
         <v>2432</v>
       </c>
-      <c r="H8" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I8" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="H8" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D9" s="7">
-        <v>38</v>
-      </c>
-      <c r="E9" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F9" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="C9" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="5">
+        <v>38</v>
+      </c>
+      <c r="E9" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F9" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G9" s="5">
         <v>2449</v>
       </c>
-      <c r="H9" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I9" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="7" t="s">
+      <c r="H9" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D10" s="7">
-        <v>38</v>
-      </c>
-      <c r="E10" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F10" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="C10" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D10" s="5">
+        <v>38</v>
+      </c>
+      <c r="E10" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F10" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G10" s="5">
         <v>2507</v>
       </c>
-      <c r="H10" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I10" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="7" t="s">
+      <c r="H10" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D11" s="7">
-        <v>38</v>
-      </c>
-      <c r="E11" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F11" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="C11" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="5">
+        <v>38</v>
+      </c>
+      <c r="E11" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F11" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G11" s="5">
         <v>2512</v>
       </c>
-      <c r="H11" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I11" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="7" t="s">
+      <c r="H11" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="7">
-        <v>38</v>
-      </c>
-      <c r="E12" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F12" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="C12" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D12" s="5">
+        <v>38</v>
+      </c>
+      <c r="E12" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F12" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G12" s="5">
         <v>1965</v>
       </c>
-      <c r="H12" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I12" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="H12" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I12" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="7">
-        <v>38</v>
-      </c>
-      <c r="E13" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F13" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G13" s="7">
+      <c r="C13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="5">
+        <v>38</v>
+      </c>
+      <c r="E13" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F13" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G13" s="5">
         <v>2288</v>
       </c>
-      <c r="H13" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I13" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="7" t="s">
+      <c r="H13" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I13" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="7">
-        <v>2025</v>
-      </c>
-      <c r="D14" s="7">
-        <v>38</v>
-      </c>
-      <c r="E14" s="8">
-        <v>45922</v>
-      </c>
-      <c r="F14" s="9">
-        <v>45926</v>
-      </c>
-      <c r="G14" s="7">
+      <c r="C14" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D14" s="5">
+        <v>38</v>
+      </c>
+      <c r="E14" s="6">
+        <v>45922</v>
+      </c>
+      <c r="F14" s="7">
+        <v>45926</v>
+      </c>
+      <c r="G14" s="5">
         <v>1452</v>
       </c>
-      <c r="H14" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I14" s="8">
-        <v>45922</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="7" t="s">
+      <c r="H14" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I14" s="6">
+        <v>45922</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Base/Backlog_38.xlsx
+++ b/Base/Backlog_38.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DCE492-F3AA-46C4-9FEA-288C242A35CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E59DC79-782F-4911-906E-679ACBD8D8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -127,9 +127,6 @@
     <t>Mara Neves</t>
   </si>
   <si>
-    <t>Jorge Acevedo</t>
-  </si>
-  <si>
     <t>Jorgenaldo Reis</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Jose Acevedo</t>
   </si>
 </sst>
 </file>
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -308,6 +308,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,7 +623,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -675,12 +675,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="13">
         <v>2025</v>
@@ -704,18 +704,18 @@
         <v>45922</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="13">
         <v>2025</v>
@@ -739,18 +739,18 @@
         <v>45922</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="13">
         <v>2025</v>
@@ -774,18 +774,18 @@
         <v>45922</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="13">
         <v>2025</v>
@@ -815,12 +815,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="13">
         <v>2025</v>
@@ -850,12 +850,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="13">
         <v>2025</v>
@@ -885,12 +885,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="13">
         <v>2025</v>
@@ -920,12 +920,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="13">
         <v>2025</v>
@@ -955,12 +955,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="13">
         <v>2025</v>
@@ -990,12 +990,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="13">
         <v>2025</v>
@@ -1025,7 +1025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>11</v>
       </c>
@@ -1060,12 +1060,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="13">
         <v>2025</v>
@@ -1095,12 +1095,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="13">
         <v>2025</v>
@@ -1130,12 +1130,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="13">
         <v>2025</v>
@@ -1159,18 +1159,18 @@
         <v>45922</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="13">
         <v>2025</v>
@@ -1200,12 +1200,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="13">
         <v>2025</v>
@@ -1235,12 +1235,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="13">
         <v>2025</v>
@@ -1264,18 +1264,18 @@
         <v>45922</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="13">
         <v>2025</v>
@@ -1305,7 +1305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>11</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>11</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>11</v>
       </c>
@@ -1439,13 +1439,13 @@
         <v>45922</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>11</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>11</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>11</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>11</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>11</v>
       </c>
@@ -1614,13 +1614,13 @@
         <v>45922</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K28" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>11</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>45922</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>13</v>
@@ -1684,18 +1684,18 @@
         <v>45922</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="13">
         <v>2025</v>
@@ -1719,18 +1719,18 @@
         <v>45922</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K31" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="13">
         <v>2025</v>
@@ -1754,18 +1754,18 @@
         <v>45922</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="13">
         <v>2025</v>
@@ -1800,7 +1800,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="13">
         <v>2025</v>
@@ -1830,12 +1830,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" s="13">
         <v>2025</v>
@@ -1865,12 +1865,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C36" s="13">
         <v>2025</v>
@@ -1894,18 +1894,18 @@
         <v>45922</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K36" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" s="13">
         <v>2025</v>
@@ -1929,18 +1929,18 @@
         <v>45922</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K37" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38" s="13">
         <v>2025</v>
@@ -1964,18 +1964,18 @@
         <v>45922</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K38" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="13">
         <v>2025</v>
@@ -1999,18 +1999,18 @@
         <v>45922</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K39" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C40" s="13">
         <v>2025</v>
@@ -2034,18 +2034,18 @@
         <v>45922</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K40" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41" s="13">
         <v>2025</v>
@@ -2069,18 +2069,18 @@
         <v>45922</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" s="13">
         <v>2025</v>
@@ -2104,18 +2104,18 @@
         <v>45922</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K42" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" s="13">
         <v>2025</v>
@@ -2139,18 +2139,18 @@
         <v>45922</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" s="13">
         <v>2025</v>
@@ -2174,18 +2174,18 @@
         <v>45922</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C45" s="13">
         <v>2025</v>
@@ -2209,18 +2209,18 @@
         <v>45922</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K45" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C46" s="13">
         <v>2025</v>
@@ -2244,18 +2244,18 @@
         <v>45922</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K46" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C47" s="13">
         <v>2025</v>
@@ -2279,18 +2279,18 @@
         <v>45922</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K47" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" s="13">
         <v>2025</v>
@@ -2314,18 +2314,18 @@
         <v>45922</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K48" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C49" s="13">
         <v>2025</v>
@@ -2349,13 +2349,13 @@
         <v>45922</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K49" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>11</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>11</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>45922</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K51" s="13" t="s">
         <v>13</v>
@@ -2429,8 +2429,8 @@
       <c r="A52" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>28</v>
+      <c r="B52" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="C52" s="13">
         <v>2025</v>
@@ -2465,7 +2465,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53" s="13">
         <v>2025</v>
@@ -2495,7 +2495,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>11</v>
       </c>
@@ -2524,18 +2524,18 @@
         <v>45922</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K54" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C55" s="13">
         <v>2025</v>
@@ -2565,12 +2565,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56" s="13">
         <v>2025</v>
@@ -2594,18 +2594,18 @@
         <v>45922</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K56" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" s="13">
         <v>2025</v>
@@ -2635,12 +2635,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C58" s="13">
         <v>2025</v>
@@ -2670,12 +2670,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="13">
         <v>2025</v>
@@ -2705,12 +2705,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60" s="13">
         <v>2025</v>
@@ -2740,12 +2740,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" s="13">
         <v>2025</v>
@@ -2816,13 +2816,7 @@
       <c r="I71" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K61" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <filterColumn colId="7">
-      <filters>
-        <dateGroupItem year="2025" month="8" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K61" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2911,7 +2905,7 @@
         <v>45922</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>23</v>
@@ -2946,7 +2940,7 @@
         <v>45922</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>23</v>
@@ -2981,7 +2975,7 @@
         <v>45922</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>23</v>
@@ -3051,7 +3045,7 @@
         <v>45922</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>23</v>
@@ -3086,7 +3080,7 @@
         <v>45922</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>23</v>
@@ -3121,7 +3115,7 @@
         <v>45922</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>23</v>
@@ -3156,7 +3150,7 @@
         <v>45922</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>23</v>
@@ -3191,7 +3185,7 @@
         <v>45922</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>23</v>
@@ -3296,7 +3290,7 @@
         <v>45922</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>23</v>
@@ -3331,7 +3325,7 @@
         <v>45922</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>23</v>

--- a/Base/Backlog_38.xlsx
+++ b/Base/Backlog_38.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E59DC79-782F-4911-906E-679ACBD8D8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0FBC44-02F9-4316-B1F9-0D089CD85B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -88,9 +88,6 @@
     <t>Edson Junior</t>
   </si>
   <si>
-    <t>Erick Silva</t>
-  </si>
-  <si>
     <t>Felipe Nascimento</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t>Jose Acevedo</t>
+  </si>
+  <si>
+    <t>Higor Cruz</t>
   </si>
 </sst>
 </file>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="13">
         <v>2025</v>
@@ -704,7 +704,7 @@
         <v>45922</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>13</v>
@@ -715,7 +715,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="13">
         <v>2025</v>
@@ -739,7 +739,7 @@
         <v>45922</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>13</v>
@@ -750,7 +750,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="13">
         <v>2025</v>
@@ -774,7 +774,7 @@
         <v>45922</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>13</v>
@@ -785,7 +785,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="13">
         <v>2025</v>
@@ -820,7 +820,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="13">
         <v>2025</v>
@@ -855,7 +855,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="13">
         <v>2025</v>
@@ -890,7 +890,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="13">
         <v>2025</v>
@@ -925,7 +925,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="13">
         <v>2025</v>
@@ -960,7 +960,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="13">
         <v>2025</v>
@@ -995,7 +995,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="13">
         <v>2025</v>
@@ -1065,7 +1065,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="13">
         <v>2025</v>
@@ -1100,7 +1100,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="13">
         <v>2025</v>
@@ -1135,7 +1135,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="13">
         <v>2025</v>
@@ -1159,7 +1159,7 @@
         <v>45922</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>13</v>
@@ -1170,7 +1170,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="13">
         <v>2025</v>
@@ -1205,7 +1205,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="13">
         <v>2025</v>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="13">
         <v>2025</v>
@@ -1264,7 +1264,7 @@
         <v>45922</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>13</v>
@@ -1275,7 +1275,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="13">
         <v>2025</v>
@@ -1310,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C20" s="13">
         <v>2025</v>
@@ -1325,7 +1325,7 @@
         <v>45926</v>
       </c>
       <c r="G20" s="13">
-        <v>1159</v>
+        <v>1564</v>
       </c>
       <c r="H20" s="17">
         <v>45901</v>
@@ -1334,7 +1334,7 @@
         <v>45922</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>13</v>
@@ -1345,7 +1345,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" s="13">
         <v>2025</v>
@@ -1360,7 +1360,7 @@
         <v>45926</v>
       </c>
       <c r="G21" s="13">
-        <v>2051</v>
+        <v>1159</v>
       </c>
       <c r="H21" s="17">
         <v>45901</v>
@@ -1380,7 +1380,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="13">
         <v>2025</v>
@@ -1395,7 +1395,7 @@
         <v>45926</v>
       </c>
       <c r="G22" s="13">
-        <v>2095</v>
+        <v>2051</v>
       </c>
       <c r="H22" s="17">
         <v>45901</v>
@@ -1415,7 +1415,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="13">
         <v>2025</v>
@@ -1430,7 +1430,7 @@
         <v>45926</v>
       </c>
       <c r="G23" s="13">
-        <v>2270</v>
+        <v>2095</v>
       </c>
       <c r="H23" s="17">
         <v>45901</v>
@@ -1439,7 +1439,7 @@
         <v>45922</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>13</v>
@@ -1450,7 +1450,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" s="13">
         <v>2025</v>
@@ -1465,7 +1465,7 @@
         <v>45926</v>
       </c>
       <c r="G24" s="13">
-        <v>2231</v>
+        <v>2270</v>
       </c>
       <c r="H24" s="17">
         <v>45901</v>
@@ -1474,7 +1474,7 @@
         <v>45922</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>13</v>
@@ -1485,7 +1485,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="13">
         <v>2025</v>
@@ -1500,7 +1500,7 @@
         <v>45926</v>
       </c>
       <c r="G25" s="13">
-        <v>2458</v>
+        <v>2231</v>
       </c>
       <c r="H25" s="17">
         <v>45901</v>
@@ -1520,7 +1520,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="13">
         <v>2025</v>
@@ -1535,7 +1535,7 @@
         <v>45926</v>
       </c>
       <c r="G26" s="13">
-        <v>1010</v>
+        <v>2458</v>
       </c>
       <c r="H26" s="17">
         <v>45901</v>
@@ -1555,7 +1555,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="13">
         <v>2025</v>
@@ -1570,7 +1570,7 @@
         <v>45926</v>
       </c>
       <c r="G27" s="13">
-        <v>1535</v>
+        <v>1010</v>
       </c>
       <c r="H27" s="17">
         <v>45901</v>
@@ -1590,7 +1590,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="13">
         <v>2025</v>
@@ -1605,7 +1605,7 @@
         <v>45926</v>
       </c>
       <c r="G28" s="13">
-        <v>1802</v>
+        <v>1535</v>
       </c>
       <c r="H28" s="17">
         <v>45901</v>
@@ -1614,7 +1614,7 @@
         <v>45922</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K28" s="13" t="s">
         <v>13</v>
@@ -1625,7 +1625,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="13">
         <v>2025</v>
@@ -1640,7 +1640,7 @@
         <v>45926</v>
       </c>
       <c r="G29" s="13">
-        <v>2010</v>
+        <v>1802</v>
       </c>
       <c r="H29" s="17">
         <v>45901</v>
@@ -1649,7 +1649,7 @@
         <v>45922</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>13</v>
@@ -1660,7 +1660,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" s="13">
         <v>2025</v>
@@ -1675,16 +1675,16 @@
         <v>45926</v>
       </c>
       <c r="G30" s="13">
-        <v>344208</v>
+        <v>2010</v>
       </c>
       <c r="H30" s="17">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I30" s="15">
         <v>45922</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>13</v>
@@ -1695,7 +1695,7 @@
         <v>11</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C31" s="13">
         <v>2025</v>
@@ -1710,16 +1710,16 @@
         <v>45926</v>
       </c>
       <c r="G31" s="13">
-        <v>2468</v>
+        <v>344208</v>
       </c>
       <c r="H31" s="17">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I31" s="15">
         <v>45922</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K31" s="13" t="s">
         <v>13</v>
@@ -1730,7 +1730,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C32" s="13">
         <v>2025</v>
@@ -1745,16 +1745,16 @@
         <v>45926</v>
       </c>
       <c r="G32" s="13">
-        <v>2518</v>
+        <v>344693</v>
       </c>
       <c r="H32" s="17">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I32" s="15">
         <v>45922</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>13</v>
@@ -1764,8 +1764,8 @@
       <c r="A33" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>29</v>
+      <c r="B33" s="21" t="s">
+        <v>34</v>
       </c>
       <c r="C33" s="13">
         <v>2025</v>
@@ -1780,10 +1780,10 @@
         <v>45926</v>
       </c>
       <c r="G33" s="13">
-        <v>1045</v>
+        <v>344437</v>
       </c>
       <c r="H33" s="17">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I33" s="15">
         <v>45922</v>
@@ -1800,7 +1800,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="13">
         <v>2025</v>
@@ -1815,16 +1815,16 @@
         <v>45926</v>
       </c>
       <c r="G34" s="13">
-        <v>344387</v>
+        <v>2468</v>
       </c>
       <c r="H34" s="17">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I34" s="15">
         <v>45922</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K34" s="13" t="s">
         <v>13</v>
@@ -1835,7 +1835,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C35" s="13">
         <v>2025</v>
@@ -1850,7 +1850,7 @@
         <v>45926</v>
       </c>
       <c r="G35" s="13">
-        <v>1720</v>
+        <v>2518</v>
       </c>
       <c r="H35" s="17">
         <v>45901</v>
@@ -1859,7 +1859,7 @@
         <v>45922</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K35" s="13" t="s">
         <v>13</v>
@@ -1870,7 +1870,7 @@
         <v>11</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C36" s="13">
         <v>2025</v>
@@ -1885,7 +1885,7 @@
         <v>45926</v>
       </c>
       <c r="G36" s="13">
-        <v>2005</v>
+        <v>1045</v>
       </c>
       <c r="H36" s="17">
         <v>45901</v>
@@ -1894,7 +1894,7 @@
         <v>45922</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K36" s="13" t="s">
         <v>13</v>
@@ -1905,7 +1905,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C37" s="13">
         <v>2025</v>
@@ -1920,16 +1920,16 @@
         <v>45926</v>
       </c>
       <c r="G37" s="13">
-        <v>2009</v>
+        <v>344387</v>
       </c>
       <c r="H37" s="17">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="I37" s="15">
         <v>45922</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K37" s="13" t="s">
         <v>13</v>
@@ -1940,7 +1940,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="13">
         <v>2025</v>
@@ -1955,7 +1955,7 @@
         <v>45926</v>
       </c>
       <c r="G38" s="13">
-        <v>2048</v>
+        <v>1720</v>
       </c>
       <c r="H38" s="17">
         <v>45901</v>
@@ -1964,7 +1964,7 @@
         <v>45922</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K38" s="13" t="s">
         <v>13</v>
@@ -1975,7 +1975,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C39" s="13">
         <v>2025</v>
@@ -1990,7 +1990,7 @@
         <v>45926</v>
       </c>
       <c r="G39" s="13">
-        <v>2054</v>
+        <v>2005</v>
       </c>
       <c r="H39" s="17">
         <v>45901</v>
@@ -1999,7 +1999,7 @@
         <v>45922</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K39" s="13" t="s">
         <v>13</v>
@@ -2010,7 +2010,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" s="13">
         <v>2025</v>
@@ -2025,7 +2025,7 @@
         <v>45926</v>
       </c>
       <c r="G40" s="13">
-        <v>2059</v>
+        <v>2009</v>
       </c>
       <c r="H40" s="17">
         <v>45901</v>
@@ -2034,7 +2034,7 @@
         <v>45922</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K40" s="13" t="s">
         <v>13</v>
@@ -2045,7 +2045,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" s="13">
         <v>2025</v>
@@ -2060,7 +2060,7 @@
         <v>45926</v>
       </c>
       <c r="G41" s="13">
-        <v>2099</v>
+        <v>2048</v>
       </c>
       <c r="H41" s="17">
         <v>45901</v>
@@ -2069,7 +2069,7 @@
         <v>45922</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>13</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C42" s="13">
         <v>2025</v>
@@ -2095,7 +2095,7 @@
         <v>45926</v>
       </c>
       <c r="G42" s="13">
-        <v>2100</v>
+        <v>2054</v>
       </c>
       <c r="H42" s="17">
         <v>45901</v>
@@ -2104,7 +2104,7 @@
         <v>45922</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K42" s="13" t="s">
         <v>13</v>
@@ -2115,7 +2115,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C43" s="13">
         <v>2025</v>
@@ -2130,7 +2130,7 @@
         <v>45926</v>
       </c>
       <c r="G43" s="13">
-        <v>2134</v>
+        <v>2059</v>
       </c>
       <c r="H43" s="17">
         <v>45901</v>
@@ -2139,7 +2139,7 @@
         <v>45922</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>13</v>
@@ -2150,7 +2150,7 @@
         <v>11</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="13">
         <v>2025</v>
@@ -2165,7 +2165,7 @@
         <v>45926</v>
       </c>
       <c r="G44" s="13">
-        <v>2156</v>
+        <v>2099</v>
       </c>
       <c r="H44" s="17">
         <v>45901</v>
@@ -2174,7 +2174,7 @@
         <v>45922</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>13</v>
@@ -2185,7 +2185,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45" s="13">
         <v>2025</v>
@@ -2200,7 +2200,7 @@
         <v>45926</v>
       </c>
       <c r="G45" s="13">
-        <v>2256</v>
+        <v>2100</v>
       </c>
       <c r="H45" s="17">
         <v>45901</v>
@@ -2209,7 +2209,7 @@
         <v>45922</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K45" s="13" t="s">
         <v>13</v>
@@ -2220,7 +2220,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46" s="13">
         <v>2025</v>
@@ -2235,7 +2235,7 @@
         <v>45926</v>
       </c>
       <c r="G46" s="13">
-        <v>2266</v>
+        <v>2134</v>
       </c>
       <c r="H46" s="17">
         <v>45901</v>
@@ -2244,7 +2244,7 @@
         <v>45922</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K46" s="13" t="s">
         <v>13</v>
@@ -2255,7 +2255,7 @@
         <v>11</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="13">
         <v>2025</v>
@@ -2270,7 +2270,7 @@
         <v>45926</v>
       </c>
       <c r="G47" s="13">
-        <v>2326</v>
+        <v>2156</v>
       </c>
       <c r="H47" s="17">
         <v>45901</v>
@@ -2279,7 +2279,7 @@
         <v>45922</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K47" s="13" t="s">
         <v>13</v>
@@ -2290,7 +2290,7 @@
         <v>11</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C48" s="13">
         <v>2025</v>
@@ -2305,7 +2305,7 @@
         <v>45926</v>
       </c>
       <c r="G48" s="13">
-        <v>2411</v>
+        <v>2256</v>
       </c>
       <c r="H48" s="17">
         <v>45901</v>
@@ -2314,7 +2314,7 @@
         <v>45922</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K48" s="13" t="s">
         <v>13</v>
@@ -2325,7 +2325,7 @@
         <v>11</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C49" s="13">
         <v>2025</v>
@@ -2340,7 +2340,7 @@
         <v>45926</v>
       </c>
       <c r="G49" s="13">
-        <v>2591</v>
+        <v>2266</v>
       </c>
       <c r="H49" s="17">
         <v>45901</v>
@@ -2349,7 +2349,7 @@
         <v>45922</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K49" s="13" t="s">
         <v>13</v>
@@ -2360,7 +2360,7 @@
         <v>11</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C50" s="13">
         <v>2025</v>
@@ -2375,7 +2375,7 @@
         <v>45926</v>
       </c>
       <c r="G50" s="13">
-        <v>2440</v>
+        <v>2326</v>
       </c>
       <c r="H50" s="17">
         <v>45901</v>
@@ -2384,7 +2384,7 @@
         <v>45922</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K50" s="13" t="s">
         <v>13</v>
@@ -2395,7 +2395,7 @@
         <v>11</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C51" s="13">
         <v>2025</v>
@@ -2410,7 +2410,7 @@
         <v>45926</v>
       </c>
       <c r="G51" s="13">
-        <v>1838</v>
+        <v>2411</v>
       </c>
       <c r="H51" s="17">
         <v>45901</v>
@@ -2419,7 +2419,7 @@
         <v>45922</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K51" s="13" t="s">
         <v>13</v>
@@ -2429,8 +2429,8 @@
       <c r="A52" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>35</v>
+      <c r="B52" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="C52" s="13">
         <v>2025</v>
@@ -2445,16 +2445,16 @@
         <v>45926</v>
       </c>
       <c r="G52" s="13">
-        <v>344437</v>
+        <v>2591</v>
       </c>
       <c r="H52" s="17">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I52" s="15">
         <v>45922</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K52" s="13" t="s">
         <v>13</v>
@@ -2465,7 +2465,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C53" s="13">
         <v>2025</v>
@@ -2480,10 +2480,10 @@
         <v>45926</v>
       </c>
       <c r="G53" s="13">
-        <v>344693</v>
+        <v>2440</v>
       </c>
       <c r="H53" s="17">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="I53" s="15">
         <v>45922</v>
@@ -2500,7 +2500,7 @@
         <v>11</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C54" s="13">
         <v>2025</v>
@@ -2515,7 +2515,7 @@
         <v>45926</v>
       </c>
       <c r="G54" s="13">
-        <v>1564</v>
+        <v>1838</v>
       </c>
       <c r="H54" s="17">
         <v>45901</v>
@@ -2524,7 +2524,7 @@
         <v>45922</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K54" s="13" t="s">
         <v>13</v>
@@ -2535,7 +2535,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="13">
         <v>2025</v>
@@ -2570,7 +2570,7 @@
         <v>11</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56" s="13">
         <v>2025</v>
@@ -2594,7 +2594,7 @@
         <v>45922</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K56" s="13" t="s">
         <v>13</v>
@@ -2605,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C57" s="13">
         <v>2025</v>
@@ -2640,7 +2640,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58" s="13">
         <v>2025</v>
@@ -2675,7 +2675,7 @@
         <v>11</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59" s="13">
         <v>2025</v>
@@ -2710,7 +2710,7 @@
         <v>11</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C60" s="13">
         <v>2025</v>
@@ -2745,7 +2745,7 @@
         <v>11</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61" s="13">
         <v>2025</v>
@@ -2816,7 +2816,11 @@
       <c r="I71" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K61" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
+  <autoFilter ref="A1:K61" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K61">
+      <sortCondition ref="B1:B61"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2878,10 +2882,10 @@
     </row>
     <row r="2" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C2" s="5">
         <v>2025</v>
@@ -2905,18 +2909,18 @@
         <v>45922</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="5">
         <v>2025</v>
@@ -2940,18 +2944,18 @@
         <v>45922</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="5">
         <v>2025</v>
@@ -2975,18 +2979,18 @@
         <v>45922</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5">
         <v>2025</v>
@@ -3013,15 +3017,15 @@
         <v>12</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C6" s="5">
         <v>2025</v>
@@ -3045,18 +3049,18 @@
         <v>45922</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5">
         <v>2025</v>
@@ -3080,18 +3084,18 @@
         <v>45922</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5">
         <v>2025</v>
@@ -3115,18 +3119,18 @@
         <v>45922</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C9" s="5">
         <v>2025</v>
@@ -3150,18 +3154,18 @@
         <v>45922</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C10" s="5">
         <v>2025</v>
@@ -3185,18 +3189,18 @@
         <v>45922</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5">
         <v>2025</v>
@@ -3223,15 +3227,15 @@
         <v>12</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="5">
         <v>2025</v>
@@ -3258,15 +3262,15 @@
         <v>12</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="5">
         <v>2025</v>
@@ -3290,18 +3294,18 @@
         <v>45922</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="5">
         <v>2025</v>
@@ -3325,10 +3329,10 @@
         <v>45922</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">

--- a/Base/Backlog_38.xlsx
+++ b/Base/Backlog_38.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0FBC44-02F9-4316-B1F9-0D089CD85B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD52193-F1C6-4E50-8285-BDF54DEE6524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -112,9 +112,6 @@
     <t>Willian Rios</t>
   </si>
   <si>
-    <t>Denis Silva</t>
-  </si>
-  <si>
     <t>Higor Jesus</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t>Higor Cruz</t>
+  </si>
+  <si>
+    <t>Denis da Silva</t>
   </si>
 </sst>
 </file>
@@ -308,7 +308,9 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,7 +682,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="13">
         <v>2025</v>
@@ -704,7 +706,7 @@
         <v>45922</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>13</v>
@@ -715,7 +717,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="13">
         <v>2025</v>
@@ -739,7 +741,7 @@
         <v>45922</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>13</v>
@@ -750,7 +752,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="13">
         <v>2025</v>
@@ -774,7 +776,7 @@
         <v>45922</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>13</v>
@@ -785,7 +787,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="13">
         <v>2025</v>
@@ -820,7 +822,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="13">
         <v>2025</v>
@@ -855,7 +857,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="13">
         <v>2025</v>
@@ -890,7 +892,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="13">
         <v>2025</v>
@@ -925,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="13">
         <v>2025</v>
@@ -960,7 +962,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="13">
         <v>2025</v>
@@ -995,7 +997,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="13">
         <v>2025</v>
@@ -1065,7 +1067,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="13">
         <v>2025</v>
@@ -1100,7 +1102,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="13">
         <v>2025</v>
@@ -1135,7 +1137,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="13">
         <v>2025</v>
@@ -1159,7 +1161,7 @@
         <v>45922</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>13</v>
@@ -1170,7 +1172,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="13">
         <v>2025</v>
@@ -1205,7 +1207,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="13">
         <v>2025</v>
@@ -1240,7 +1242,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="13">
         <v>2025</v>
@@ -1264,7 +1266,7 @@
         <v>45922</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>13</v>
@@ -1275,7 +1277,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="13">
         <v>2025</v>
@@ -1310,7 +1312,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="13">
         <v>2025</v>
@@ -1334,7 +1336,7 @@
         <v>45922</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>13</v>
@@ -1474,7 +1476,7 @@
         <v>45922</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>13</v>
@@ -1649,7 +1651,7 @@
         <v>45922</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>13</v>
@@ -1684,7 +1686,7 @@
         <v>45922</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>13</v>
@@ -1719,7 +1721,7 @@
         <v>45922</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K31" s="13" t="s">
         <v>13</v>
@@ -1730,7 +1732,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32" s="13">
         <v>2025</v>
@@ -1765,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="13">
         <v>2025</v>
@@ -1800,7 +1802,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="13">
         <v>2025</v>
@@ -1824,7 +1826,7 @@
         <v>45922</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K34" s="13" t="s">
         <v>13</v>
@@ -1835,7 +1837,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" s="13">
         <v>2025</v>
@@ -1859,7 +1861,7 @@
         <v>45922</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K35" s="13" t="s">
         <v>13</v>
@@ -1870,7 +1872,7 @@
         <v>11</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" s="13">
         <v>2025</v>
@@ -1905,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="13">
         <v>2025</v>
@@ -1940,7 +1942,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C38" s="13">
         <v>2025</v>
@@ -1975,7 +1977,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" s="13">
         <v>2025</v>
@@ -1999,7 +2001,7 @@
         <v>45922</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K39" s="13" t="s">
         <v>13</v>
@@ -2010,7 +2012,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" s="13">
         <v>2025</v>
@@ -2034,7 +2036,7 @@
         <v>45922</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K40" s="13" t="s">
         <v>13</v>
@@ -2045,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" s="13">
         <v>2025</v>
@@ -2069,7 +2071,7 @@
         <v>45922</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>13</v>
@@ -2080,7 +2082,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" s="13">
         <v>2025</v>
@@ -2104,7 +2106,7 @@
         <v>45922</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K42" s="13" t="s">
         <v>13</v>
@@ -2115,7 +2117,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43" s="13">
         <v>2025</v>
@@ -2139,7 +2141,7 @@
         <v>45922</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>13</v>
@@ -2150,7 +2152,7 @@
         <v>11</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44" s="13">
         <v>2025</v>
@@ -2174,7 +2176,7 @@
         <v>45922</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>13</v>
@@ -2185,7 +2187,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45" s="13">
         <v>2025</v>
@@ -2209,7 +2211,7 @@
         <v>45922</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K45" s="13" t="s">
         <v>13</v>
@@ -2220,7 +2222,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="13">
         <v>2025</v>
@@ -2244,7 +2246,7 @@
         <v>45922</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K46" s="13" t="s">
         <v>13</v>
@@ -2255,7 +2257,7 @@
         <v>11</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47" s="13">
         <v>2025</v>
@@ -2279,7 +2281,7 @@
         <v>45922</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K47" s="13" t="s">
         <v>13</v>
@@ -2290,7 +2292,7 @@
         <v>11</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48" s="13">
         <v>2025</v>
@@ -2314,7 +2316,7 @@
         <v>45922</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K48" s="13" t="s">
         <v>13</v>
@@ -2325,7 +2327,7 @@
         <v>11</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" s="13">
         <v>2025</v>
@@ -2349,7 +2351,7 @@
         <v>45922</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K49" s="13" t="s">
         <v>13</v>
@@ -2360,7 +2362,7 @@
         <v>11</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C50" s="13">
         <v>2025</v>
@@ -2384,7 +2386,7 @@
         <v>45922</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K50" s="13" t="s">
         <v>13</v>
@@ -2395,7 +2397,7 @@
         <v>11</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51" s="13">
         <v>2025</v>
@@ -2419,7 +2421,7 @@
         <v>45922</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K51" s="13" t="s">
         <v>13</v>
@@ -2430,7 +2432,7 @@
         <v>11</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" s="13">
         <v>2025</v>
@@ -2454,7 +2456,7 @@
         <v>45922</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K52" s="13" t="s">
         <v>13</v>
@@ -2524,7 +2526,7 @@
         <v>45922</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K54" s="13" t="s">
         <v>13</v>
@@ -2535,7 +2537,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C55" s="13">
         <v>2025</v>
@@ -2570,7 +2572,7 @@
         <v>11</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C56" s="13">
         <v>2025</v>
@@ -2594,7 +2596,7 @@
         <v>45922</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K56" s="13" t="s">
         <v>13</v>
@@ -2605,7 +2607,7 @@
         <v>11</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C57" s="13">
         <v>2025</v>
@@ -2640,7 +2642,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58" s="13">
         <v>2025</v>
@@ -2675,7 +2677,7 @@
         <v>11</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C59" s="13">
         <v>2025</v>
@@ -2710,7 +2712,7 @@
         <v>11</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C60" s="13">
         <v>2025</v>
@@ -2745,7 +2747,7 @@
         <v>11</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C61" s="13">
         <v>2025</v>
@@ -2909,7 +2911,7 @@
         <v>45922</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>22</v>
@@ -2944,7 +2946,7 @@
         <v>45922</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>22</v>
@@ -2955,7 +2957,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C4" s="5">
         <v>2025</v>
@@ -2979,7 +2981,7 @@
         <v>45922</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>22</v>
@@ -2990,7 +2992,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5">
         <v>2025</v>
@@ -3025,7 +3027,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="5">
         <v>2025</v>
@@ -3049,7 +3051,7 @@
         <v>45922</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>22</v>
@@ -3060,7 +3062,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="5">
         <v>2025</v>
@@ -3084,7 +3086,7 @@
         <v>45922</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>22</v>
@@ -3095,7 +3097,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5">
         <v>2025</v>
@@ -3119,7 +3121,7 @@
         <v>45922</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>22</v>
@@ -3130,7 +3132,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5">
         <v>2025</v>
@@ -3154,7 +3156,7 @@
         <v>45922</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>22</v>
@@ -3165,7 +3167,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="5">
         <v>2025</v>
@@ -3189,7 +3191,7 @@
         <v>45922</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>22</v>
@@ -3200,7 +3202,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5">
         <v>2025</v>
@@ -3235,7 +3237,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5">
         <v>2025</v>
@@ -3270,7 +3272,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5">
         <v>2025</v>
@@ -3294,7 +3296,7 @@
         <v>45922</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>22</v>
@@ -3305,7 +3307,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5">
         <v>2025</v>
@@ -3329,7 +3331,7 @@
         <v>45922</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>22</v>
